--- a/SahibindenProject/input/SahibindenIlanlar 1.xlsx
+++ b/SahibindenProject/input/SahibindenIlanlar 1.xlsx
@@ -101,7 +101,118 @@
     <x:t>Column-7 Url</x:t>
   </x:si>
   <x:si>
-    <x:t>KARŞIYAKADA YENİ YAPI 2+0 DAYALI DÖŞELİ</x:t>
+    <x:t>YENİ YAPILAN TOKİ'LERDE KİRALIK 3+1 EŞYALI DAİRE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3+1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20 Ağustos
+2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kahta
+Yavuz Selim Mah.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.sahibinden.com/kiralik/adiyaman-kahta?price_min=10000&amp;price_max=50000#</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MUSTAFA KEMAL CADDESİ ÜZERİNDE KİRALIK 2+1 DAİRE ARA KAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>130</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2+1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kahta
+Turgut Özal Mh.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAVUZ SELİM MAHALLESİNDE (HASTANE CADDESİNDE) 2+1 KİRALIK DAİRE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOKİ'DE KİRALIK 3+1 DAİRE 135 m2 MUSA MEZARLIK YANİ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19 Ağustos
+2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kiralık daire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.500 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kahta
+Girne Mah.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Yeni yapılan salkımbağ emlak konutlarında kiralık daire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>110</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Köyler
+Salkımbağı Köyü</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YILMAZ EMLAK'TAN ATATÜRK MAH. KİRALIK 3+1 DAİRE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>140</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18 Ağustos
+2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kahta
+Atatürk Mh.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EŞYALI DAYALİ DÖŞELİ DAİRE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.500 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17 Ağustos
+2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KİRALIK 2+0 dayalı döşeli SIFIR daire</x:t>
   </x:si>
   <x:si>
     <x:t>75</x:t>
@@ -110,257 +221,142 @@
     <x:t>2+0</x:t>
   </x:si>
   <x:si>
-    <x:t>15.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05 Ağustos
-2025</x:t>
+    <x:t>16.000 TL</x:t>
   </x:si>
   <x:si>
     <x:t>Kahta
 Karşıyaka Mh.</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.sahibinden.com/kiralik/adiyaman-kahta?price_min=10000&amp;price_max=50000#</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOKİ'LERDE KİRALIK DAİRE</x:t>
+    <x:t>Toki 3+1 sıfır daire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>108</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16 Ağustos
+2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sıfır Daire sahibinden</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiralık Full eşyalı 2+0 Daire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15 Ağustos
+2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GÜVEN EMLAK'TAN YAVUZ SELİM MAHALLESİNDE KİRALIK BAHÇE KATI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>170</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13 Ağustos
+2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiralık daire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12 Ağustos
+2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alüt Salkımbağı bağı toki</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11 Ağustos
+2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kiralık yeni mah 3+1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10 Ağustos
+2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kahta
+Yeni Mah.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KANTİK EMLAK KİRALIK 2+1 Açıklamayı Okuyunuz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08 Ağustos
+2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kahta
+Fırat Mh.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HASTANE ACİL ÇAPRAZI FULL ESYALI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1+1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07 Ağustos
+2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTIN EMLAK'TAN KİRALIK MERKEZİ KONUMDA 2+1 DAİRE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06 Ağustos
+2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kahta
+Menderes Mah.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Adliye karşısı ana cadde üzerinde kiralık daire</x:t>
   </x:si>
   <x:si>
     <x:t>125</x:t>
   </x:si>
   <x:si>
-    <x:t>3+1</x:t>
+    <x:t>24 Temmuz
+2025</x:t>
   </x:si>
   <x:si>
     <x:t>Kahta
-Turgut Özal Mh.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MUSTAFA KEMAL CADDESİ ÜZERİNDE KİRALIK 2+1 DAİRE ARA KAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>130</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2+1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>kiralık 3+1 daire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.500 TL</x:t>
+Fatih Mah.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>satılık hobi bahcesi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>400</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stüdyo (1+0)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>550.000 TL</x:t>
   </x:si>
   <x:si>
     <x:t>03 Ağustos
 2025</x:t>
   </x:si>
   <x:si>
-    <x:t>Kahta
-Fatih Mah.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Son 3 gün! Sahibinden Açık Otopark Konut Yok 4+1 Merkeze 5 dk Uzaklıkta</x:t>
-  </x:si>
-  <x:si>
-    <x:t>220</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4+1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03 Ağustos
-                            2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KahtaMenderes Mah.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Turgut Özal mah. 2+1 kiralık</x:t>
-  </x:si>
-  <x:si>
-    <x:t>120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kiralık müstakil daire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kahta
-Menderes Mah.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KİRALIK MÜSTAKİL BAHÇE KATI LÜTFEN AÇIKLAMAYI OKUYUN!!!!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kahta
-Hürriyet Mh.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Yeni TOKİ'de sıfır 3+1 daire sahibinden</x:t>
-  </x:si>
-  <x:si>
-    <x:t>140</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02 Ağustos
-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kahta
-Girne Mah.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kiralık 240 m2 4+1 lüx daire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>240</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kahta
-Fırat Mh.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARŞIYAKA MAH MEHMET AKİF CAD ANA CADDE AÇIK CEPHE 3+1 DAİRE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18.500 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YILMAZ EMLAK'TAN SALKIMBAĞI TOKİ KONUTLARI KİRALIK 3+1 DAİRE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>110</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12.500 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01 Ağustos
-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Köyler
-Salkımbağı Köyü</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hastane caddesinde 2+1 ara kat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31 Temmuz
-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kahta
-Yavuz Selim Mah.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Yavuzselim mahallesi kiralık 2+1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTIN EMLAK'TAN ÇARŞI MERKEZDE KİRALIK EŞYALI 1+1 DAİRE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>55</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1+1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30 Temmuz
-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kiralık eşyalı 1+1 hastane caddesinde 1 katta</x:t>
-  </x:si>
-  <x:si>
-    <x:t>50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Çobanlı Mah.Nazarkent Sitesinde Kiralık Daire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29 Temmuz
-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Köyler
-Çobanlı Mh.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kiralık 1+1 Temmuz 5 temmuzda teslim edilecek</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sahibinden Kiralık Daire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>170</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENDERES MAH. KİRALIK 3+1 DAİRE 180 m2 İ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25 Temmuz
-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Adliye karşısı ana cadde üzerinde kiralık daire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24 Temmuz
-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>satılık hobi bahcesi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>400</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Stüdyo (1+0)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>550.000 TL</x:t>
-  </x:si>
-  <x:si>
     <x:t>Altındağ
 Kavaklı Mh.</x:t>
   </x:si>
@@ -371,35 +367,191 @@
     <x:t>Malatya, Battalgazi için istenilen Sonuç Bulunamadı.</x:t>
   </x:si>
   <x:si>
-    <x:t>Üsküdar Fıstıkağacında Sıfır Binada 2+1 Asansörlü Otoparklı 1Kat</x:t>
+    <x:t>Emin'den,Zeynepkam­il,3+2,Dubleks,Te­raslı,kombili,çift cephe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3+2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.100.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Merkez
+Zeynep Kamil Mah.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.sahibinden.com/satilik/istanbul-uskudar?price_min=400000&amp;price_max=10000000#</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tütenemlak'ta­nFıstıkağacı Bakkaladem Sk. ÖzelBahçeli Boş Y.giriş</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.950.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bağlarbaşı
+Selami Ali Mah.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIRSATTIR,ALIRKEN KAZANMAK İSTEYEN ACELE ETSİN!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.145.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Acıbadem
+Acıbadem Mh.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ÜSKÜDAR BULGURLU MERKEZDE METROYA KOMŞU 3+1 110M2 NET ARA KAT !!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.650.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bulgurlu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Beylerbeyi Burhaniye Metrobüs Yanı Kelepir Bahçeli Ters Dubleks</x:t>
   </x:si>
   <x:si>
     <x:t>80</x:t>
   </x:si>
   <x:si>
-    <x:t>9.500.000 TL</x:t>
+    <x:t>4.850.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Beylerbeyi
+Burhaniye Mah.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ÜSKÜDAR BAĞLARBAŞINDA MASRAFSIZ, BALKONLU 2+1 ARA KAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.150.000 TL</x:t>
   </x:si>
   <x:si>
     <x:t>Bağlarbaşı
-Murat Reis Mah.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.sahibinden.com/satilik/istanbul-uskudar?price_min=400000&amp;price_max=10000000#</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tütenemlak"­tanİcadiye Ayarcıbaşı Sk.ta Mükemmel Lokasyon Temiz</x:t>
-  </x:si>
-  <x:si>
-    <x:t>95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.250.000 TL</x:t>
+Valide-i Atik Mh.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5+2 DUBLEKS-3+1 FİYATINA-2 AYRI DAİRE TEK TAPULU-GÜZEL KONUMDA..</x:t>
+  </x:si>
+  <x:si>
+    <x:t>200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5+2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.500.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bulgurlu
+Cumhuriyet Mah.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANKA'dan BULGURLU'da GERÇEK KONUM, GERÇEK FIRSAT 2+1 DAİRE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.950.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Fiyatı Düşürüldü !! Yatırımlık 1+1 Üsküdar Ünalan'da Metro 5 dk.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.895.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ünalan
+Ünalan Mh.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ÖZEL İNSANLARA GÜZEL DAİRELER... LİBADİYE'DE 2+1 1.KAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.700.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KISIKLI DA SIFIR SATILIK 2+1 DAİRE....</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.900.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ferah
+Kısıklı Mh.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIRSAT! PRESTİJLİ LÜKS DAİRE ŞİMDİ UYGUN FİYATLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.750.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ÜSKÜDAR İCADİYEDE, CUMHURİYET CADDESİ ÜZERİNDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.500.000 TL</x:t>
   </x:si>
   <x:si>
     <x:t>Bağlarbaşı
 İcadiye Mh.</x:t>
   </x:si>
   <x:si>
+    <x:t>ÜSKÜDAR BULGURLU'DA 5+1 DUBLEX DAİRE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>220</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5+1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.500.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLUHİSARI KÜÇÜKSU OFİSKENT SİTESİ BAHÇE KATI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.100.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28 Temmuz
+2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kandilli
+Küçüksu Mh.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Siz de ilanınızın yukarıda yer almasını istiyorsanız tıklayın.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.sahibinden.com/doping-tanitim/#doping-5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VALİDEİ ATİK MAHALLESİ-PAZARBAŞI SOKAK SATILIK 3+1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.540.000 TL</x:t>
+  </x:si>
+  <x:si>
     <x:t>SON İNDİRİMLİ! İCADİYE' DE HARİKA BAHÇE KULLANIMLI 1+1 DAİRE</x:t>
   </x:si>
   <x:si>
@@ -409,196 +561,39 @@
     <x:t>6.475.000 TL</x:t>
   </x:si>
   <x:si>
-    <x:t>SIFIR SÜPERDUBLEKS EMSALLERİNEGÖRE ÇOK UYGUN FİYAT 4+1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.000.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ünalan
-Ünalan Mh.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMİR'DEN TEK TETKİLİ ÜSKÜDAR KÜÇÜK ÇAMLICA MAHLLESİNDE DUBLEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.250.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Çamlıca
-Küçük Çamlıca Mh.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LİBADİYE BULGURLU MAH.3+1 130m2 İÇİ TEMİZ ARA KAT SATILIK DAİRE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.500.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bulgurlu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ŞEHR-İ ÜSKÜDAR'DA Kİ EVİNİZ BİZDEN BU AY IÇIN SON FIYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.600.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Merkez
-Aziz Mahmut Hüdayi Mh.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAVUZTÜRK BOSNABULVARI'NA YAKIN YATIRIMLIK 3+1 150m² GENİŞ DAİRE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.935.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27 Temmuz
-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ferah
-Yavuztürk Mh.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Fiyat DÜŞTÜ MASRAFSIZ SATILIK 2+1 DAİRE ÜSKÜDAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.550.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bağlarbaşı
-Valide-i Atik Mh.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Üsküdar Merkezde Cadde Üzerinde 2+1 85M 3Kat Kaplı Cephesi Yok</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.800.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Merkez
-Sultantepe Mah.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAĞLARBAŞINDA METRO YA ÇOK YAKIN SIFIR 2+1 BAHÇE KATI DAİRE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.850.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23 Temmuz
-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGURLU NAMAZGAH'TA METROYA YAKIN SATILIK 3+2 DUBLEKS DAİRE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>195</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22 Temmuz
-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMEK EMLAK'TAN ÜSKÜDAR ÜNALAN MAH.DE SATILIK 2+1 YENİ DAİRE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.750.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19 Temmuz
-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CUMHURİYET CADDESİ ÜZERİNDE FISTIKAĞACI METROYA 1 DK , 0 DAİRE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Var Daire 2+1 Son 3 gün! Çok Uygun Kaçırılmayacak Fırsat! Bahçe Katı</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02 Ağustos
-                            2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MerkezSalacak Mah.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VADİ YAVUZTÜRK EVLERİNDE 2+1 SİTE İÇİNDE DAİRE SATILIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>86</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.020.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18 Temmuz
-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Parlak ' tan Üsküdar Bağlarbaşında 4+2 Keyifli Teraslı Dublex</x:t>
-  </x:si>
-  <x:si>
-    <x:t>210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4+2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.300.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13 Temmuz
-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Üsküdar Selami Ali'De 2+1 80m² Balkonlu Satılık Yüksek Giriş</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.800.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bağlarbaşı
-Selami Ali Mah.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACİLSATILIKTIR SIFIR DAİRE KOMBİ ANKASTRE AYRIMUTFAK SIFIR 2+1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12 Temmuz
-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLDEN HOMES'TAN SALACAK MAHALLESİNDE ÇOK KEYİFLİ 1+1 DAİRE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10 Temmuz
-2025</x:t>
+    <x:t>Fırsat !! Beylerbeyi merkezde acil 3+1 Satılık Daire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>115</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.200.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Beylerbeyi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ÜSKÜDAR SALACAK 3+1 SATILIK DAİRE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.200.000 TL</x:t>
   </x:si>
   <x:si>
     <x:t>Merkez
 Salacak Mah.</x:t>
   </x:si>
   <x:si>
-    <x:t>METROYA ÇOK YAKIN KREDİYE UYGUN KATTA TEK 3+1 SATILIK DAİRE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.600.000 TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09 Temmuz
-2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Siz de ilanınızın yukarıda yer almasını istiyorsanız tıklayın.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.sahibinden.com/doping-tanitim/#doping-5</x:t>
+    <x:t>Altunizadede Güvenlikli Site İçerisinde 3+1 Daire EMLAK MASASI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.200.000 TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Altunizade
+Barbaros Mah.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1109,13 +1104,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
         <x:v>29</x:v>
@@ -1123,22 +1118,22 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
         <x:v>29</x:v>
@@ -1146,22 +1141,22 @@
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
         <x:v>29</x:v>
@@ -1175,16 +1170,16 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s">
+      <x:c r="E7" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
         <x:v>29</x:v>
@@ -1192,22 +1187,22 @@
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
+      <x:c r="E8" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
         <x:v>29</x:v>
@@ -1215,22 +1210,22 @@
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
+      <x:c r="C9" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
+      <x:c r="F9" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
         <x:v>29</x:v>
@@ -1238,22 +1233,22 @@
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
         <x:v>29</x:v>
@@ -1267,16 +1262,16 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
         <x:v>29</x:v>
@@ -1284,22 +1279,22 @@
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
         <x:v>29</x:v>
@@ -1310,16 +1305,16 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>28</x:v>
@@ -1330,22 +1325,22 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="E14" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
         <x:v>29</x:v>
@@ -1353,22 +1348,22 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
         <x:v>29</x:v>
@@ -1376,22 +1371,22 @@
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
         <x:v>29</x:v>
@@ -1399,22 +1394,22 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
         <x:v>29</x:v>
@@ -1422,22 +1417,22 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
         <x:v>29</x:v>
@@ -1445,22 +1440,22 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
         <x:v>29</x:v>
@@ -1468,22 +1463,22 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
         <x:v>29</x:v>
@@ -1491,22 +1486,22 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
         <x:v>29</x:v>
@@ -1514,22 +1509,22 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
         <x:v>29</x:v>
@@ -1537,22 +1532,22 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
         <x:v>29</x:v>
@@ -1600,25 +1595,25 @@
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
+      <x:c r="F2" s="0" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="G2" s="0" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>104</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1640,7 +1635,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:1">
       <x:c r="A1" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1685,209 +1680,209 @@
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
+      <x:c r="E7" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>123</x:v>
-      </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
         <x:v>135</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
@@ -1895,229 +1890,229 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>139</x:v>
-      </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="B13" s="0" t="s">
+      <x:c r="G13" s="0" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="G13" s="0" t="s">
-        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="G17" s="0" t="s">
-        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
         <x:v>157</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>161</x:v>
-      </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="B20" s="0" t="s">
+      <x:c r="E20" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="C20" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="F20" s="0" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="G20" s="0" t="s">
-        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
       <x:c r="E21" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="F21" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
@@ -2125,68 +2120,68 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
